--- a/registration_forms/042_virtual_shopping_assistant_demo_registration--registration_forms.xlsx
+++ b/registration_forms/042_virtual_shopping_assistant_demo_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1094,7 +1094,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1111,7 +1111,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1145,7 +1145,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1196,7 +1196,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1213,7 +1213,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1230,7 +1230,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
